--- a/human_resources_forms/016_free_background_check_authorization_form_template--human_resources_forms.xlsx
+++ b/human_resources_forms/016_free_background_check_authorization_form_template--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>employee_number</t>
+          <t>Employee Number Two</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>Date Of Birth Two</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Address Two</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>Date Of Birth Three</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>Date Of Birth Four</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>date_of_birth_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>Date Of Birth 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>date_of_birth_two</t>
+          <t>date_of_birth_two_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>Date Of Birth Two 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>date_of_birth_three</t>
+          <t>date_of_birth_three_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>Date Of Birth Three 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Note Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Note Three</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Note Four</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Note Five</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Note Six</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Note Seven</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Note Eight</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1006,12 +1006,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1124,216 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>select_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>select_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>option5</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>option5</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>select_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>option6</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>option6</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>select_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>option7</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>option7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>option8</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>option8</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>option9</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>option9</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>option10</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>option10</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option11</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>option11</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>option12</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option13</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>option13</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option14</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>option14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option15</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>option15</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
